--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -97,14 +97,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -415,10 +415,10 @@
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
     <col min="2" max="2" width="11.90625" customWidth="1"/>
-    <col min="3" max="3" width="29.7265625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="29.7265625" style="4" customWidth="1"/>
     <col min="4" max="4" width="22.90625" customWidth="1"/>
     <col min="5" max="5" width="29.6328125" customWidth="1"/>
-    <col min="6" max="6" width="27.26953125" customWidth="1"/>
+    <col min="6" max="6" width="27.26953125" style="4" customWidth="1"/>
     <col min="7" max="7" width="24.7265625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -429,7 +429,7 @@
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -438,7 +438,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28130" windowHeight="12540"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,16 +29,18 @@
     <t>产品登记编码*</t>
   </si>
   <si>
-    <t>巨额赎回日期（YYYY-MM-DD)*</t>
-  </si>
-  <si>
     <t>触发的情形说明文字*</t>
   </si>
   <si>
     <t>拒绝赎回说明（文字）*</t>
   </si>
   <si>
-    <t>报告发布日期（YYYY-MM-DD)*</t>
+    <t>巨额赎回日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报告发布日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -411,18 +413,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" customWidth="1"/>
-    <col min="3" max="3" width="29.7265625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.90625" customWidth="1"/>
-    <col min="5" max="5" width="29.6328125" customWidth="1"/>
-    <col min="6" max="6" width="27.26953125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="24.7265625" customWidth="1"/>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11.875" customWidth="1"/>
+    <col min="3" max="3" width="29.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="29.625" customWidth="1"/>
+    <col min="6" max="6" width="27.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -430,13 +432,13 @@
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>5</v>
@@ -452,7 +454,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -463,7 +465,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro001.xlsx
@@ -99,13 +99,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro001.xlsx
@@ -29,9 +29,6 @@
     <t>产品登记编码*</t>
   </si>
   <si>
-    <t>触发的情形说明文字*</t>
-  </si>
-  <si>
     <t>拒绝赎回说明（文字）*</t>
   </si>
   <si>
@@ -40,6 +37,10 @@
   </si>
   <si>
     <t>报告发布日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发的情形说明文字（文字）*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -418,7 +419,7 @@
     <col min="1" max="1" width="16.375" customWidth="1"/>
     <col min="2" max="2" width="11.875" customWidth="1"/>
     <col min="3" max="3" width="29.75" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
     <col min="5" max="5" width="29.625" customWidth="1"/>
     <col min="6" max="6" width="27.25" style="4" customWidth="1"/>
     <col min="7" max="7" width="24.75" customWidth="1"/>
@@ -432,16 +433,16 @@
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/HugeInfoPro001.xlsx
@@ -21,12 +21,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>产品子代码*</t>
-  </si>
-  <si>
-    <t>产品登记编码*</t>
   </si>
   <si>
     <t>拒绝赎回说明（文字）*</t>
@@ -413,36 +410,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11.875" customWidth="1"/>
-    <col min="3" max="3" width="29.75" style="4" customWidth="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1"/>
-    <col min="5" max="5" width="29.625" customWidth="1"/>
-    <col min="6" max="6" width="27.25" style="4" customWidth="1"/>
-    <col min="7" max="7" width="24.75" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="2" width="29.75" style="4" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="29.625" customWidth="1"/>
+    <col min="5" max="5" width="27.25" style="4" customWidth="1"/>
+    <col min="6" max="6" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
